--- a/sources/spi.xlsx
+++ b/sources/spi.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>NORTHERN STAR RESOURCES LIMITED</t>
+          <t>OWNER</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KCGM GROWTH PROJECT</t>
+          <t>GROWTH PROJECT</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23517</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slurry Hose - Fimiston SAG Mill Discharge 90Deg Bend</t>
+          <t>Slurry Hose - FIM SAG Mill Discharge 90Deg Bend</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Slurry Hose - Fimiston SAG Mill Discharge 45Deg Bend</t>
+          <t>Slurry Hose - FIM SAG Mill Discharge 45Deg Bend</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Slurry Hose - Fimiston SAG Mill Discharge 90Deg Bend w/ Extension 1</t>
+          <t>Slurry Hose - FIM SAG Mill Discharge 90Deg Bend w/ Extension 1</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -14111,7 +14111,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Slurry Hose - Fimiston SAG Mill Discharge 90Deg Bend w/ Extension 2</t>
+          <t>Slurry Hose - FIM SAG Mill Discharge 90Deg Bend w/ Extension 2</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>23517-18-0941-FS-RL3-500-01_0</t>
+          <t>18-0941-FS-RL3-500-01_0</t>
         </is>
       </c>
       <c r="BC165" t="n">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t xml:space="preserve">MMS oxygen injectors are available on a monthly rental basis. They are not available for sale. KCGM may elect to enter a month by month, one or two year oxygen injector rental agreement with MMS. Rental rates are discounted as the rental term increases &amp;/or the number of units rented increases. </t>
+          <t xml:space="preserve">MMS oxygen injectors are available on a monthly rental basis. They are not available for sale. Owner may elect to enter a month by month, one or two year oxygen injector rental agreement with MMS. Rental rates are discounted as the rental term increases &amp;/or the number of units rented increases. </t>
         </is>
       </c>
       <c r="DS177" t="n">
@@ -25005,7 +25005,7 @@
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t xml:space="preserve">MMS oxygen injectors are available on a monthly rental basis. They are not available for sale. KCGM may elect to enter a month by month, one or two year oxygen injector rental agreement with MMS. Rental rates are discounted as the rental term increases &amp;/or the number of units rented increases. </t>
+          <t xml:space="preserve">MMS oxygen injectors are available on a monthly rental basis. They are not available for sale. Owner may elect to enter a month by month, one or two year oxygen injector rental agreement with MMS. Rental rates are discounted as the rental term increases &amp;/or the number of units rented increases. </t>
         </is>
       </c>
       <c r="DS234" t="n">
